--- a/output/pdf_financials_xlsx/RSI.xlsx
+++ b/output/pdf_financials_xlsx/RSI.xlsx
@@ -2403,10 +2403,10 @@
         <v>1.246</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>17.033</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>2.101</v>
       </c>
       <c r="K34" s="1" t="inlineStr">
         <is>
@@ -2419,16 +2419,16 @@
         </is>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.151</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>19.121</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>8.545</v>
       </c>
     </row>
     <row r="35">
@@ -2515,10 +2515,10 @@
         <v>1.246</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>17.033</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>2.101</v>
       </c>
       <c r="K36" s="1" t="inlineStr">
         <is>
@@ -2531,16 +2531,16 @@
         </is>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.151</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>19.121</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>8.545</v>
       </c>
     </row>
     <row r="37">
@@ -3187,10 +3187,10 @@
         <v>3.132</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>21.059</v>
+        <v>4.026</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>6.757</v>
+        <v>4.656</v>
       </c>
       <c r="K48" s="1" t="inlineStr">
         <is>
@@ -3203,16 +3203,16 @@
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>23.697</v>
+        <v>23.546</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>16.257</v>
+        <v>16.211</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>32.266</v>
+        <v>13.145</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>19.944</v>
+        <v>11.399</v>
       </c>
     </row>
     <row r="49">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -30712,7 +30712,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">

--- a/output/pdf_financials_xlsx/RSI.xlsx
+++ b/output/pdf_financials_xlsx/RSI.xlsx
@@ -1094,13 +1094,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-0</v>
+        <v>-15.361</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0</v>
+        <v>-9.695</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>-9.127000000000001</v>
       </c>
       <c r="F13" s="1" t="inlineStr">
         <is>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0</v>
+        <v>-11.931</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-0</v>
+        <v>-9.612</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>-0</v>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-0</v>
+        <v>-18.523</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0</v>
+        <v>-19.439</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>-0</v>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="O13" s="3" t="n">
-        <v>-0</v>
+        <v>-47.566</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>-0</v>
+        <v>-47.004</v>
       </c>
     </row>
     <row r="14">
@@ -2002,13 +2002,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>53.523</v>
+        <v>68.884</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>40.909</v>
+        <v>50.604</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>50.411</v>
+        <v>59.538</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>32.539</v>
+        <v>44.47</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>89.191</v>
+        <v>98.803</v>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>49.684</v>
+        <v>68.20699999999999</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>65.05800000000001</v>
+        <v>84.497</v>
       </c>
       <c r="M27" s="1" t="inlineStr">
         <is>
@@ -2048,10 +2048,10 @@
         </is>
       </c>
       <c r="O27" s="3" t="n">
-        <v>73.426</v>
+        <v>120.992</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>86.29900000000001</v>
+        <v>133.303</v>
       </c>
     </row>
     <row r="28">
@@ -2066,13 +2066,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.138</v>
+        <v>11.409</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.177</v>
+        <v>11.861</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.23</v>
+        <v>12.587</v>
       </c>
       <c r="F28" s="1" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.199</v>
+        <v>12.918</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>13.596</v>
@@ -2124,13 +2124,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>53.661</v>
+        <v>80.29300000000001</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>41.086</v>
+        <v>62.465</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>50.641</v>
+        <v>72.125</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -2138,10 +2138,10 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>32.738</v>
+        <v>57.388</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>102.787</v>
+        <v>112.399</v>
       </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>49.684</v>
+        <v>68.20699999999999</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>65.05800000000001</v>
+        <v>84.497</v>
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>73.426</v>
+        <v>120.992</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>86.29900000000001</v>
+        <v>133.303</v>
       </c>
     </row>
     <row r="30">
@@ -2188,13 +2188,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>8.759349280297219</v>
+        <v>13.10662178794477</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>6.64721975495597</v>
+        <v>10.10608435947341</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>9.0683298772648</v>
+        <v>12.91548927544329</v>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>6.045296328098311</v>
+        <v>10.59708796129592</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>15.05999117970688</v>
+        <v>16.46830774911101</v>
       </c>
       <c r="I30" s="1" t="inlineStr">
         <is>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>5.77183344350204</v>
+        <v>7.92366644555478</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>7.277742913043624</v>
+        <v>9.452295535114008</v>
       </c>
       <c r="M30" s="1" t="inlineStr">
         <is>
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="O30" s="3" t="n">
-        <v>5.961049325235455</v>
+        <v>9.822668808853653</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>6.574515723787909</v>
+        <v>10.15542091482056</v>
       </c>
     </row>
     <row r="31">
@@ -6078,13 +6078,13 @@
         </is>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>11.409</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>11.861</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>12.587</v>
       </c>
       <c r="F100" s="1" t="inlineStr">
         <is>
@@ -6092,10 +6092,10 @@
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>12.918</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>12.345</v>
       </c>
       <c r="I100" s="1" t="inlineStr">
         <is>
@@ -6118,10 +6118,10 @@
         </is>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>3.865</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>3.806</v>
       </c>
       <c r="O100" s="1" t="inlineStr">
         <is>
@@ -57636,7 +57636,7 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
@@ -60042,7 +60042,11 @@
           <t>Additions to intangible assets (note 12)</t>
         </is>
       </c>
-      <c r="D577" t="inlineStr"/>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E577" t="inlineStr">
         <is>
           <t>-</t>
@@ -60863,7 +60867,11 @@
           <t>Depreciation of property, plant and equipment (note 4)</t>
         </is>
       </c>
-      <c r="D586" t="inlineStr"/>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E586" t="inlineStr">
         <is>
           <t>-</t>
@@ -62111,7 +62119,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D600" t="inlineStr"/>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E600" t="inlineStr">
         <is>
           <t>-</t>
@@ -66376,7 +66388,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D647" t="inlineStr"/>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E647" t="inlineStr">
         <is>
           <t>-</t>
@@ -67392,7 +67408,11 @@
           <t>Net finance costs (note 5)</t>
         </is>
       </c>
-      <c r="D659" t="inlineStr"/>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E659" t="inlineStr">
         <is>
           <t>-</t>
@@ -69759,7 +69779,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D686" t="inlineStr"/>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E686" t="inlineStr">
         <is>
           <t>-</t>
@@ -73268,7 +73292,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D725" t="inlineStr"/>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E725" t="inlineStr">
         <is>
           <t>-</t>
@@ -79220,7 +79248,11 @@
           <t>Net Finance costs</t>
         </is>
       </c>
-      <c r="D791" t="inlineStr"/>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E791" t="inlineStr">
         <is>
           <t>-</t>
